--- a/output/resultados_pipeline.xlsx
+++ b/output/resultados_pipeline.xlsx
@@ -1,13 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Validacion_Rangos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validacion_Rangos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validacion_Reglas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distribuciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulacion" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,14 +473,14 @@
         <v>272.11</v>
       </c>
       <c r="D2" t="n">
-        <v>263.56</v>
+        <v>42.22530401859531</v>
       </c>
       <c r="E2" t="n">
-        <v>272.11</v>
+        <v>474.627977821469</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>OK: Dentro de rango</t>
+          <t>FUERA: Fuera de rango (Ambos extremos)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -495,14 +502,14 @@
         <v>788.41</v>
       </c>
       <c r="D3" t="n">
-        <v>774.38</v>
+        <v>531.7173554454332</v>
       </c>
       <c r="E3" t="n">
-        <v>788.41</v>
+        <v>1404.906385163981</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>OK: Dentro de rango</t>
+          <t>FUERA: Fuera de rango (Ambos extremos)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -524,14 +531,14 @@
         <v>403.35</v>
       </c>
       <c r="D4" t="n">
-        <v>401.19</v>
+        <v>-771.7002868988308</v>
       </c>
       <c r="E4" t="n">
-        <v>403.35</v>
+        <v>1185.176938492109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>OK: Dentro de rango</t>
+          <t>FUERA: Fuera de rango (Ambos extremos)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -553,14 +560,14 @@
         <v>538.88</v>
       </c>
       <c r="D5" t="n">
-        <v>535.14</v>
+        <v>-22.90401168624214</v>
       </c>
       <c r="E5" t="n">
-        <v>538.88</v>
+        <v>1149.750369159052</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OK: Dentro de rango</t>
+          <t>FUERA: Fuera de rango (Ambos extremos)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -582,14 +589,14 @@
         <v>174.16</v>
       </c>
       <c r="D6" t="n">
-        <v>171.45</v>
+        <v>172.2460484796832</v>
       </c>
       <c r="E6" t="n">
-        <v>174.16</v>
+        <v>174.5587715883424</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>OK: Dentro de rango</t>
+          <t>ALTO: Sobre el maximo esperado</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -611,14 +618,14 @@
         <v>166.8</v>
       </c>
       <c r="D7" t="n">
-        <v>164.26</v>
+        <v>78395.73333866177</v>
       </c>
       <c r="E7" t="n">
-        <v>166.8</v>
+        <v>78395.73905019241</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BAJO: Bajo el minimo esperado</t>
+          <t>ALTO: Sobre el maximo esperado</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -640,19 +647,3794 @@
         <v>30.38</v>
       </c>
       <c r="D8" t="n">
-        <v>29.51</v>
+        <v>10722.89637505839</v>
       </c>
       <c r="E8" t="n">
-        <v>30.38</v>
+        <v>10722.90544553609</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OK: Dentro de rango</t>
+          <t>ALTO: Sobre el maximo esperado</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Cálculo pendiente (Métrica de severidad)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Acero_CrMoV_LimFluencia</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>350</v>
+      </c>
+      <c r="C9" t="n">
+        <v>450</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sin datos de muestra</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Acero_CrMoV_ResFatiga</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>150</v>
+      </c>
+      <c r="C10" t="n">
+        <v>230</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sin datos de muestra</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Acero_CrMoV_ModElasticidad</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>190</v>
+      </c>
+      <c r="C11" t="n">
+        <v>210</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Sin datos de muestra</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Regla</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Detalle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Presión no negativa</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pres_domo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Variable no encontrada</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>La variable 'pres_domo' no esta en los datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Presión no negativa</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pres_vap_sobrecal_a_turbina</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Variable no encontrada</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>La variable 'pres_vap_sobrecal_a_turbina' no esta en los datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Presión no negativa</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pres_vapor_entrada_recalentador</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Variable no encontrada</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>La variable 'pres_vapor_entrada_recalentador' no esta en los datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Temperatura de diseño</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>temp_vapor_sobrecalentado_despues_atemperador_izq</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Variable no encontrada</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>La variable 'temp_vapor_sobrecalentado_despues_atemperador_izq' no esta en los datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Temperatura de diseño</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>temp_vapor_recalentado_salida_caldera</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Variable no encontrada</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>La variable 'temp_vapor_recalentado_salida_caldera' no esta en los datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Turbina apagada - Potencia cero</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Multiples</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Error de evaluacion</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Variable 'flujo_vapor_sobrecalentado_cuerpo_ap_turbina' no encontrada</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID_Tecnico</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Distribucion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Param1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Param2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Param3</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>GOF_Metric</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>GOF_Value</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Tipo_en_modelo</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Mecanismos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Weibull</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>269.6288128208678</v>
+      </c>
+      <c r="D2" t="n">
+        <v>132.3727849202127</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7061678941221792</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>forma=132.3728, escala=269.6288</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>potencia_activa</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Vibraciones_mecanicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Weibull</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>785.3536373718186</v>
+      </c>
+      <c r="D3" t="n">
+        <v>321.4122878177411</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9841682434440797</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>forma=321.4123, escala=785.3536</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>flujo_vapor_sobrecalentado</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>t/h</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>SPE,Choque_termico,Fatiga_termica</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Weibull</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>402.6115044578474</v>
+      </c>
+      <c r="D4" t="n">
+        <v>685.848632438771</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3447330198005294</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>forma=685.8486, escala=402.6115</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>temp_vapor_sobrecalentado_atemperador</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Choque_termico,Fatiga_termica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Weibull</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>537.6151409643667</v>
+      </c>
+      <c r="D5" t="n">
+        <v>479.2347993303979</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4765286128298802</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>forma=479.2348, escala=537.6151</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>temp_vapor_recalentado_salida</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Creep,Fatiga_termica,SPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>173.2685714285714</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.6067892527714327</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9740530589738302</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>mu=173.2686, sigma=0.6068</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>presion_domo</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Creep,SCC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>78395.73567416596</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.002116186532001251</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.956949756483743</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>forma=78395.7357, escala=0.0021</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>presion_vapor_sobrecalentado_turbina</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>SPE,Creep</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Gamma</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10722.9010828852</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.002799349040443278</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7114887391817304</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>forma=10722.9011, escala=0.0028</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>presion_vapor_entrada_recalentador</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Creep,Fatiga</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D169"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ID_Tecnico</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tipo_en_modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46123.72774701018</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>269.6288128208678</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46123.76941367686</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>305.1699933136221</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46123.81108034352</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>254.3135762101227</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46123.85274701018</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>304.3125500843455</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46123.89441367686</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>237.2211071485387</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46123.93608034352</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>144.4002763864394</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46123.97774701018</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>114.7800128587182</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46124.01941367686</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>159.0337217746234</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46124.06108034352</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>451.3728289291957</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46124.10274701018</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>393.3801043324184</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46124.14441367686</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>474.627977821469</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46124.18608034352</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>459.8616832713456</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46124.22774701018</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>384.4572580381425</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46124.26941367686</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>326.1086406497663</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46124.31108034352</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>408.0983567490935</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46124.35274701018</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>397.4048864316246</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46124.39441367686</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>420.1648654721669</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46124.43608034352</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>377.0765851242837</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46124.47774701018</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>288.1655216316455</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46124.51941367686</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>293.4012950595113</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46124.56108034352</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>335.7452954128414</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46124.60274701018</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>227.9499472779486</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46124.64441367686</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>99.35014806605977</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46124.68608034352</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1GEV007CE</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>42.22530401859531</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46123.72774701018</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>785.3536373718186</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46123.76941367686</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1213.090558806623</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46123.81108034352</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1104.67036840497</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46123.85274701018</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1077.853884711452</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46123.89441367686</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1304.226085207814</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46123.93608034352</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1380.184882526544</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46123.97774701018</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1404.906385163981</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46124.01941367686</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1112.17983896604</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46124.06108034352</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1111.795433870323</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46124.10274701018</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1003.429017099873</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46124.14441367686</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1145.766126066075</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46124.18608034352</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1172.423760795282</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46124.22774701018</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1039.773953894767</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46124.26941367686</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1095.776341355866</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46124.31108034352</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>825.6224606840323</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>46124.35274701018</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>802.3802911974476</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>46124.39441367686</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>531.7173554454332</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>46124.43608034352</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>670.5197864754223</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>46124.47774701018</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1016.274355553926</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>46124.51941367686</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>770.5530579697577</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>46124.56108034352</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>911.589450922355</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46124.60274701018</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1128.228517852581</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46124.64441367686</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1023.476117220523</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>46124.68608034352</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1FSRFTB504</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>654.2223478879332</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>46123.72774701018</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>402.6115044578474</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>46123.76941367686</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>105.7667978036031</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>46123.81108034352</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>-415.4628384272092</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>46123.85274701018</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>-43.41098628679163</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>46123.89441367686</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>158.7579656032548</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>46123.93608034352</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>351.9130165342936</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>46123.97774701018</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>275.5453342119202</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>46124.01941367686</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>-771.7002868988308</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>46124.06108034352</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>85.72840503597655</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>46124.10274701018</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>746.544987034152</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>46124.14441367686</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>-71.81922163324487</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>46124.18608034352</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1081.854169765878</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>46124.22774701018</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>-14.97497195176277</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>46124.26941367686</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>-210.3978923336135</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>46124.31108034352</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>241.0948340986795</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>46124.35274701018</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>-58.86738248883916</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>46124.39441367686</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>-13.42239926471925</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>46124.43608034352</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>312.1430738966261</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>46124.47774701018</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>49.36979341834137</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>46124.51941367686</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>330.6283737783075</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>46124.56108034352</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>517.8441072195321</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>46124.60274701018</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>374.3674369941132</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>46124.64441367686</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1185.176938492109</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46124.68608034352</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1FSRTE502C</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>802.1004321320465</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>46123.72774701018</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>537.6151409643667</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>46123.76941367686</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>593.1901724769597</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>46123.81108034352</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>969.8430929044262</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>46123.85274701018</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>557.1431824031343</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46123.89441367686</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>721.9185035781979</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>46123.93608034352</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>158.2745089088103</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>46123.97774701018</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>147.8174911381844</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46124.01941367686</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>-22.90401168624214</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46124.06108034352</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>536.7854131676791</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>46124.10274701018</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>591.1758948006554</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>46124.14441367686</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>673.7727036383485</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>46124.18608034352</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>638.4347801928045</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>46124.22774701018</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>824.5124656371274</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>46124.26941367686</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>627.1563481287055</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>46124.31108034352</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1027.184645940539</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>46124.35274701018</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>788.0685351434956</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>46124.39441367686</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1149.750369159052</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>46124.43608034352</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>615.0794212039693</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>46124.47774701018</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>635.3850202405985</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>46124.51941367686</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>590.8962241170832</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>46124.56108034352</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>322.6343573486608</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>46124.60274701018</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>464.1549012880747</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>46124.64441367686</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>220.8548715804849</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>46124.68608034352</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1FRSTE503A</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>174.8778257882903</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>46123.72774701018</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>173.2685714285714</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>46123.76941367686</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>173.88474391783</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>46123.81108034352</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>172.7060017171282</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>46123.85274701018</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>172.5563418412268</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>46123.89441367686</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>172.5746331943608</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46123.93608034352</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>172.666708136879</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>46123.97774701018</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>172.2460484796832</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>46124.01941367686</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>172.5919681918879</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>46124.06108034352</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>173.5632445305947</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>46124.10274701018</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>174.0339016055864</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>46124.14441367686</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>173.7595628558509</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>46124.18608034352</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>172.9938401226801</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>46124.22774701018</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>172.7014000210189</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>46124.26941367686</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>172.5662261300219</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>46124.31108034352</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>172.6546832616073</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>46124.35274701018</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>172.7784954595769</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>46124.39441367686</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>173.0443748877278</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>46124.43608034352</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>173.4465102832752</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>46124.47774701018</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>173.5884981131306</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>46124.51941367686</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>173.5589652369931</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>46124.56108034352</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>173.5062524633942</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>46124.60274701018</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>174.0319436304794</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>46124.64441367686</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>173.5549362059826</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>46124.68608034352</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1FSRPT501</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>174.5587715883424</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>46123.72774701018</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>78395.73567416596</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>46123.76941367686</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>78395.73586888269</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46123.81108034352</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>78395.73616105107</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46123.85274701018</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>78395.7369299729</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46123.89441367686</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>78395.73688932009</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>46123.93608034352</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>78395.73887511253</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>46123.97774701018</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>78395.73905019241</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>46124.01941367686</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>78395.73834477205</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>46124.06108034352</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>78395.73539261994</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>46124.10274701018</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>78395.73559910442</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>46124.14441367686</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>78395.73333866177</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>46124.18608034352</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>78395.73496844726</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>46124.22774701018</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>78395.73781848677</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>46124.26941367686</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>78395.73381076012</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>46124.31108034352</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>78395.73607452781</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>46124.35274701018</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>78395.73650637308</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>46124.39441367686</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>78395.73703784194</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>46124.43608034352</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>78395.73777611849</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>46124.47774701018</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>78395.7380162933</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>46124.51941367686</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>78395.73710147841</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>46124.56108034352</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>78395.73740041451</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>46124.60274701018</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>78395.73650085329</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>46124.64441367686</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>78395.73372654409</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>46124.68608034352</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1FSRPT504</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>78395.73469866991</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>46123.72774701018</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>10722.9010828852</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>46123.76941367686</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>10722.90258197768</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>46123.81108034352</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>10722.90296102731</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>46123.85274701018</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>10722.90325710325</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>46123.89441367686</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>10722.90544553609</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>46123.93608034352</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>10722.90314522651</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>46123.97774701018</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>10722.90251256508</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>46124.01941367686</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>10722.8998500097</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>46124.06108034352</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>10722.89675672445</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>46124.10274701018</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>10722.89717525208</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>46124.14441367686</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>10722.89906021708</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>46124.18608034352</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>10722.90166287348</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>46124.22774701018</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>10722.89820495686</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>46124.26941367686</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>10722.89975994197</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>46124.31108034352</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>10722.89991542579</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>46124.35274701018</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>10722.90205780944</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>46124.39441367686</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>10722.90091338286</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>46124.43608034352</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>10722.89747062301</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>46124.47774701018</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>10722.89681579333</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>46124.51941367686</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>10722.89637505839</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>46124.56108034352</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>10722.90024515133</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>46124.60274701018</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>10722.90531684987</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>46124.64441367686</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>10722.90228183091</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Carga</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>46124.68608034352</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>1FRSPT526</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>10722.90264758247</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Carga</t>
         </is>
       </c>
     </row>

--- a/output/resultados_pipeline.xlsx
+++ b/output/resultados_pipeline.xlsx
@@ -473,10 +473,10 @@
         <v>272.11</v>
       </c>
       <c r="D2" t="n">
-        <v>42.22530401859531</v>
+        <v>21.19919977630151</v>
       </c>
       <c r="E2" t="n">
-        <v>474.627977821469</v>
+        <v>378.7353576719507</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -502,10 +502,10 @@
         <v>788.41</v>
       </c>
       <c r="D3" t="n">
-        <v>531.7173554454332</v>
+        <v>164.4886878822145</v>
       </c>
       <c r="E3" t="n">
-        <v>1404.906385163981</v>
+        <v>1288.873368070933</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -531,10 +531,10 @@
         <v>403.35</v>
       </c>
       <c r="D4" t="n">
-        <v>-771.7002868988308</v>
+        <v>-212.1059589136317</v>
       </c>
       <c r="E4" t="n">
-        <v>1185.176938492109</v>
+        <v>1354.155185459261</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -560,10 +560,10 @@
         <v>538.88</v>
       </c>
       <c r="D5" t="n">
-        <v>-22.90401168624214</v>
+        <v>-32.65574919770216</v>
       </c>
       <c r="E5" t="n">
-        <v>1149.750369159052</v>
+        <v>1748.276552094443</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -589,10 +589,10 @@
         <v>174.16</v>
       </c>
       <c r="D6" t="n">
-        <v>172.2460484796832</v>
+        <v>171.6543958196061</v>
       </c>
       <c r="E6" t="n">
-        <v>174.5587715883424</v>
+        <v>174.2907769312583</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -618,10 +618,10 @@
         <v>166.8</v>
       </c>
       <c r="D7" t="n">
-        <v>78395.73333866177</v>
+        <v>78395.73364205913</v>
       </c>
       <c r="E7" t="n">
-        <v>78395.73905019241</v>
+        <v>78395.73980933517</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -647,10 +647,10 @@
         <v>30.38</v>
       </c>
       <c r="D8" t="n">
-        <v>10722.89637505839</v>
+        <v>10722.89660414125</v>
       </c>
       <c r="E8" t="n">
-        <v>10722.90544553609</v>
+        <v>10722.90602426518</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46123.72774701018</v>
+        <v>46132.61557789268</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46123.76941367686</v>
+        <v>46132.65724455935</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>305.1699933136221</v>
+        <v>378.7353576719507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46123.81108034352</v>
+        <v>46132.69891122602</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>254.3135762101227</v>
+        <v>258.0484662073902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46123.85274701018</v>
+        <v>46132.74057789268</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>304.3125500843455</v>
+        <v>150.358263314736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46123.89441367686</v>
+        <v>46132.78224455935</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>237.2211071485387</v>
+        <v>175.6400473943921</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46123.93608034352</v>
+        <v>46132.82391122602</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>144.4002763864394</v>
+        <v>345.1803963988398</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46123.97774701018</v>
+        <v>46132.86557789268</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>114.7800128587182</v>
+        <v>339.401242048662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46124.01941367686</v>
+        <v>46132.90724455935</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>159.0337217746234</v>
+        <v>83.15384234908095</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46124.06108034352</v>
+        <v>46132.94891122602</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>451.3728289291957</v>
+        <v>21.19919977630151</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46124.10274701018</v>
+        <v>46132.99057789268</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>393.3801043324184</v>
+        <v>83.9922814601117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46124.14441367686</v>
+        <v>46133.03224455935</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>474.627977821469</v>
+        <v>114.6991261254157</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46124.18608034352</v>
+        <v>46133.07391122602</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>459.8616832713456</v>
+        <v>76.54642463120608</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46124.22774701018</v>
+        <v>46133.11557789268</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>384.4572580381425</v>
+        <v>113.9543955987703</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46124.26941367686</v>
+        <v>46133.15724455935</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>326.1086406497663</v>
+        <v>151.346944671785</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46124.31108034352</v>
+        <v>46133.19891122602</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>408.0983567490935</v>
+        <v>300.6646970161923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46124.35274701018</v>
+        <v>46133.24057789268</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>397.4048864316246</v>
+        <v>255.6095158029468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46124.39441367686</v>
+        <v>46133.28224455935</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>420.1648654721669</v>
+        <v>348.232104267125</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46124.43608034352</v>
+        <v>46133.32391122602</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>377.0765851242837</v>
+        <v>312.7379338289178</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46124.47774701018</v>
+        <v>46133.36557789268</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>288.1655216316455</v>
+        <v>224.885831785583</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46124.51941367686</v>
+        <v>46133.40724455935</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>293.4012950595113</v>
+        <v>274.7227164316979</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46124.56108034352</v>
+        <v>46133.44891122602</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>335.7452954128414</v>
+        <v>232.5357028000414</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46124.60274701018</v>
+        <v>46133.49057789268</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>227.9499472779486</v>
+        <v>298.8882287133302</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46124.64441367686</v>
+        <v>46133.53224455935</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>99.35014806605977</v>
+        <v>191.4077052605048</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46124.68608034352</v>
+        <v>46133.57391122602</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>42.22530401859531</v>
+        <v>172.774144309021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46123.72774701018</v>
+        <v>46132.61557789268</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46123.76941367686</v>
+        <v>46132.65724455935</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1213.090558806623</v>
+        <v>625.1531043680753</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46123.81108034352</v>
+        <v>46132.69891122602</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1104.67036840497</v>
+        <v>622.9799583695244</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46123.85274701018</v>
+        <v>46132.74057789268</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1077.853884711452</v>
+        <v>1030.760566456234</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46123.89441367686</v>
+        <v>46132.78224455935</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1304.226085207814</v>
+        <v>1288.873368070933</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46123.93608034352</v>
+        <v>46132.82391122602</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1380.184882526544</v>
+        <v>1060.310823506587</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46123.97774701018</v>
+        <v>46132.86557789268</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1404.906385163981</v>
+        <v>1156.760056698378</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46124.01941367686</v>
+        <v>46132.90724455935</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1112.17983896604</v>
+        <v>619.8335270812262</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46124.06108034352</v>
+        <v>46132.94891122602</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1111.795433870323</v>
+        <v>581.5129058889598</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46124.10274701018</v>
+        <v>46132.99057789268</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1003.429017099873</v>
+        <v>302.6083569045732</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46124.14441367686</v>
+        <v>46133.03224455935</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1145.766126066075</v>
+        <v>614.0927295365343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46124.18608034352</v>
+        <v>46133.07391122602</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1172.423760795282</v>
+        <v>631.6106425515518</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46124.22774701018</v>
+        <v>46133.11557789268</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1039.773953894767</v>
+        <v>727.9944338697414</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46124.26941367686</v>
+        <v>46133.15724455935</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1095.776341355866</v>
+        <v>507.5663952466676</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46124.31108034352</v>
+        <v>46133.19891122602</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>825.6224606840323</v>
+        <v>164.4886878822145</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46124.35274701018</v>
+        <v>46133.24057789268</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>802.3802911974476</v>
+        <v>565.6370407758516</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46124.39441367686</v>
+        <v>46133.28224455935</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>531.7173554454332</v>
+        <v>865.2230498804739</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46124.43608034352</v>
+        <v>46133.32391122602</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>670.5197864754223</v>
+        <v>1095.619063031209</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46124.47774701018</v>
+        <v>46133.36557789268</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1016.274355553926</v>
+        <v>1190.090124279159</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46124.51941367686</v>
+        <v>46133.40724455935</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>770.5530579697577</v>
+        <v>1047.563736659842</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46124.56108034352</v>
+        <v>46133.44891122602</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>911.589450922355</v>
+        <v>1113.163092158158</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46124.60274701018</v>
+        <v>46133.49057789268</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1128.228517852581</v>
+        <v>1223.806265316895</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46124.64441367686</v>
+        <v>46133.53224455935</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1023.476117220523</v>
+        <v>1215.152678761094</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46124.68608034352</v>
+        <v>46133.57391122602</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>654.2223478879332</v>
+        <v>1203.072709717305</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46123.72774701018</v>
+        <v>46132.61557789268</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46123.76941367686</v>
+        <v>46132.65724455935</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>105.7667978036031</v>
+        <v>280.2774048723262</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46123.81108034352</v>
+        <v>46132.69891122602</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-415.4628384272092</v>
+        <v>113.0352522474203</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46123.85274701018</v>
+        <v>46132.74057789268</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-43.41098628679163</v>
+        <v>74.03245807103001</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46123.89441367686</v>
+        <v>46132.78224455935</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>158.7579656032548</v>
+        <v>363.7029087148381</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46123.93608034352</v>
+        <v>46132.82391122602</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>351.9130165342936</v>
+        <v>-209.1465255601414</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46123.97774701018</v>
+        <v>46132.86557789268</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>275.5453342119202</v>
+        <v>141.2450617042272</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46124.01941367686</v>
+        <v>46132.90724455935</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-771.7002868988308</v>
+        <v>452.1640832733412</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46124.06108034352</v>
+        <v>46132.94891122602</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>85.72840503597655</v>
+        <v>958.4810093737725</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46124.10274701018</v>
+        <v>46132.99057789268</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>746.544987034152</v>
+        <v>527.856857945197</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46124.14441367686</v>
+        <v>46133.03224455935</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-71.81922163324487</v>
+        <v>908.6566480871204</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46124.18608034352</v>
+        <v>46133.07391122602</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1081.854169765878</v>
+        <v>1255.628069706857</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46124.22774701018</v>
+        <v>46133.11557789268</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-14.97497195176277</v>
+        <v>447.0241662785144</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46124.26941367686</v>
+        <v>46133.15724455935</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-210.3978923336135</v>
+        <v>1354.155185459261</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46124.31108034352</v>
+        <v>46133.19891122602</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>241.0948340986795</v>
+        <v>1313.652467830101</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46124.35274701018</v>
+        <v>46133.24057789268</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-58.86738248883916</v>
+        <v>633.3793105684524</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46124.39441367686</v>
+        <v>46133.28224455935</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-13.42239926471925</v>
+        <v>726.0319293069507</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46124.43608034352</v>
+        <v>46133.32391122602</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>312.1430738966261</v>
+        <v>432.4242494950687</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46124.47774701018</v>
+        <v>46133.36557789268</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>49.36979341834137</v>
+        <v>-209.4567484920909</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46124.51941367686</v>
+        <v>46133.40724455935</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>330.6283737783075</v>
+        <v>-72.87209317964945</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46124.56108034352</v>
+        <v>46133.44891122602</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>517.8441072195321</v>
+        <v>365.7468386641939</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46124.60274701018</v>
+        <v>46133.49057789268</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>374.3674369941132</v>
+        <v>1136.638703618267</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46124.64441367686</v>
+        <v>46133.53224455935</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1185.176938492109</v>
+        <v>495.9957090557568</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46124.68608034352</v>
+        <v>46133.57391122602</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>802.1004321320465</v>
+        <v>-212.1059589136317</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46123.72774701018</v>
+        <v>46132.61557789268</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46123.76941367686</v>
+        <v>46132.65724455935</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>593.1901724769597</v>
+        <v>321.8419737769282</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46123.81108034352</v>
+        <v>46132.69891122602</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>969.8430929044262</v>
+        <v>1039.771081877889</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46123.85274701018</v>
+        <v>46132.74057789268</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>557.1431824031343</v>
+        <v>446.9748995886088</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46123.89441367686</v>
+        <v>46132.78224455935</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>721.9185035781979</v>
+        <v>782.7342434732643</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46123.93608034352</v>
+        <v>46132.82391122602</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>158.2745089088103</v>
+        <v>335.8583290995799</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46123.97774701018</v>
+        <v>46132.86557789268</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>147.8174911381844</v>
+        <v>271.4636357742057</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46124.01941367686</v>
+        <v>46132.90724455935</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-22.90401168624214</v>
+        <v>579.3439268106097</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46124.06108034352</v>
+        <v>46132.94891122602</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>536.7854131676791</v>
+        <v>342.5648971907864</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46124.10274701018</v>
+        <v>46132.99057789268</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>591.1758948006554</v>
+        <v>254.702497310965</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46124.14441367686</v>
+        <v>46133.03224455935</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>673.7727036383485</v>
+        <v>391.070984766288</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46124.18608034352</v>
+        <v>46133.07391122602</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>638.4347801928045</v>
+        <v>163.3099579145708</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46124.22774701018</v>
+        <v>46133.11557789268</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>824.5124656371274</v>
+        <v>375.0346716082803</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46124.26941367686</v>
+        <v>46133.15724455935</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>627.1563481287055</v>
+        <v>303.8465582443854</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46124.31108034352</v>
+        <v>46133.19891122602</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1027.184645940539</v>
+        <v>-32.65574919770216</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46124.35274701018</v>
+        <v>46133.24057789268</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>788.0685351434956</v>
+        <v>1056.572611376936</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46124.39441367686</v>
+        <v>46133.28224455935</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1149.750369159052</v>
+        <v>1748.276552094443</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46124.43608034352</v>
+        <v>46133.32391122602</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>615.0794212039693</v>
+        <v>1247.794104647778</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46124.47774701018</v>
+        <v>46133.36557789268</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>635.3850202405985</v>
+        <v>1289.73769399716</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46124.51941367686</v>
+        <v>46133.40724455935</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>590.8962241170832</v>
+        <v>543.5488687681928</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46124.56108034352</v>
+        <v>46133.44891122602</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>322.6343573486608</v>
+        <v>531.2855362540992</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46124.60274701018</v>
+        <v>46133.49057789268</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>464.1549012880747</v>
+        <v>582.8000350637012</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46124.64441367686</v>
+        <v>46133.53224455935</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>220.8548715804849</v>
+        <v>264.3162830536818</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46124.68608034352</v>
+        <v>46133.57391122602</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>174.8778257882903</v>
+        <v>465.1352490433404</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46123.72774701018</v>
+        <v>46132.61557789268</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46123.76941367686</v>
+        <v>46132.65724455935</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>173.88474391783</v>
+        <v>173.2068284406205</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46123.81108034352</v>
+        <v>46132.69891122602</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>172.7060017171282</v>
+        <v>173.6487322803842</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46123.85274701018</v>
+        <v>46132.74057789268</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>172.5563418412268</v>
+        <v>173.5705410660505</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46123.89441367686</v>
+        <v>46132.78224455935</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>172.5746331943608</v>
+        <v>173.4757545812794</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46123.93608034352</v>
+        <v>46132.82391122602</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>172.666708136879</v>
+        <v>173.4943084139711</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46123.97774701018</v>
+        <v>46132.86557789268</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>172.2460484796832</v>
+        <v>174.2907769312583</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46124.01941367686</v>
+        <v>46132.90724455935</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>172.5919681918879</v>
+        <v>174.1925937028971</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46124.06108034352</v>
+        <v>46132.94891122602</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>173.5632445305947</v>
+        <v>173.3355319790082</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46124.10274701018</v>
+        <v>46132.99057789268</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>174.0339016055864</v>
+        <v>172.7693550559703</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46124.14441367686</v>
+        <v>46133.03224455935</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>173.7595628558509</v>
+        <v>173.4899296694502</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46124.18608034352</v>
+        <v>46133.07391122602</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>172.9938401226801</v>
+        <v>173.5601685808894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46124.22774701018</v>
+        <v>46133.11557789268</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>172.7014000210189</v>
+        <v>173.4924016817116</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46124.26941367686</v>
+        <v>46133.15724455935</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>172.5662261300219</v>
+        <v>173.7868065502392</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46124.31108034352</v>
+        <v>46133.19891122602</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>172.6546832616073</v>
+        <v>173.5731286092423</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46124.35274701018</v>
+        <v>46133.24057789268</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>172.7784954595769</v>
+        <v>172.9580824968671</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46124.39441367686</v>
+        <v>46133.28224455935</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>173.0443748877278</v>
+        <v>172.7746265242732</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46124.43608034352</v>
+        <v>46133.32391122602</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>173.4465102832752</v>
+        <v>173.2137496768654</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46124.47774701018</v>
+        <v>46133.36557789268</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>173.5884981131306</v>
+        <v>173.1495932807287</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46124.51941367686</v>
+        <v>46133.40724455935</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>173.5589652369931</v>
+        <v>173.0990536121209</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46124.56108034352</v>
+        <v>46133.44891122602</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>173.5062524633942</v>
+        <v>173.1167388630959</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46124.60274701018</v>
+        <v>46133.49057789268</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>174.0319436304794</v>
+        <v>172.8979259675519</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46124.64441367686</v>
+        <v>46133.53224455935</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>173.5549362059826</v>
+        <v>172.6352777608197</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46124.68608034352</v>
+        <v>46133.57391122602</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>174.5587715883424</v>
+        <v>171.6543958196061</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46123.72774701018</v>
+        <v>46132.61557789268</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46123.76941367686</v>
+        <v>46132.65724455935</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>78395.73586888269</v>
+        <v>78395.73762872678</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46123.81108034352</v>
+        <v>46132.69891122602</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>78395.73616105107</v>
+        <v>78395.73678958294</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46123.85274701018</v>
+        <v>46132.74057789268</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>78395.7369299729</v>
+        <v>78395.73546486086</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46123.89441367686</v>
+        <v>46132.78224455935</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>78395.73688932009</v>
+        <v>78395.73744840342</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46123.93608034352</v>
+        <v>46132.82391122602</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>78395.73887511253</v>
+        <v>78395.73713985788</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46123.97774701018</v>
+        <v>46132.86557789268</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>78395.73905019241</v>
+        <v>78395.73863147084</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46124.01941367686</v>
+        <v>46132.90724455935</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>78395.73834477205</v>
+        <v>78395.73660035389</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46124.06108034352</v>
+        <v>46132.94891122602</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>78395.73539261994</v>
+        <v>78395.73606692745</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46124.10274701018</v>
+        <v>46132.99057789268</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>78395.73559910442</v>
+        <v>78395.73364205913</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46124.14441367686</v>
+        <v>46133.03224455935</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>78395.73333866177</v>
+        <v>78395.73639644647</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46124.18608034352</v>
+        <v>46133.07391122602</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>78395.73496844726</v>
+        <v>78395.73750660315</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46124.22774701018</v>
+        <v>46133.11557789268</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>78395.73781848677</v>
+        <v>78395.73980933517</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46124.26941367686</v>
+        <v>46133.15724455935</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>78395.73381076012</v>
+        <v>78395.73717105546</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46124.31108034352</v>
+        <v>46133.19891122602</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>78395.73607452781</v>
+        <v>78395.7367708502</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46124.35274701018</v>
+        <v>46133.24057789268</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>78395.73650637308</v>
+        <v>78395.7387356774</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46124.39441367686</v>
+        <v>46133.28224455935</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>78395.73703784194</v>
+        <v>78395.7378264002</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46124.43608034352</v>
+        <v>46133.32391122602</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>78395.73777611849</v>
+        <v>78395.73745154725</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46124.47774701018</v>
+        <v>46133.36557789268</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>78395.7380162933</v>
+        <v>78395.73602135852</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46124.51941367686</v>
+        <v>46133.40724455935</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>78395.73710147841</v>
+        <v>78395.73718753007</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46124.56108034352</v>
+        <v>46133.44891122602</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>78395.73740041451</v>
+        <v>78395.73860753227</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46124.60274701018</v>
+        <v>46133.49057789268</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>78395.73650085329</v>
+        <v>78395.73961239068</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46124.64441367686</v>
+        <v>46133.53224455935</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>78395.73372654409</v>
+        <v>78395.73745042527</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46124.68608034352</v>
+        <v>46133.57391122602</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>78395.73469866991</v>
+        <v>78395.73721809349</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46123.72774701018</v>
+        <v>46132.61557789268</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46123.76941367686</v>
+        <v>46132.65724455935</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>10722.90258197768</v>
+        <v>10722.89972683937</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46123.81108034352</v>
+        <v>46132.69891122602</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>10722.90296102731</v>
+        <v>10722.90223478041</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46123.85274701018</v>
+        <v>46132.74057789268</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>10722.90325710325</v>
+        <v>10722.90381338235</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46123.89441367686</v>
+        <v>46132.78224455935</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>10722.90544553609</v>
+        <v>10722.90395073709</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46123.93608034352</v>
+        <v>46132.82391122602</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>10722.90314522651</v>
+        <v>10722.90354225011</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46123.97774701018</v>
+        <v>46132.86557789268</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>10722.90251256508</v>
+        <v>10722.90543662063</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46124.01941367686</v>
+        <v>46132.90724455935</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>10722.8998500097</v>
+        <v>10722.90238178049</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46124.06108034352</v>
+        <v>46132.94891122602</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>10722.89675672445</v>
+        <v>10722.89969747775</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46124.10274701018</v>
+        <v>46132.99057789268</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>10722.89717525208</v>
+        <v>10722.90191314567</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46124.14441367686</v>
+        <v>46133.03224455935</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>10722.89906021708</v>
+        <v>10722.90444425503</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46124.18608034352</v>
+        <v>46133.07391122602</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>10722.90166287348</v>
+        <v>10722.89810178433</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46124.22774701018</v>
+        <v>46133.11557789268</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>10722.89820495686</v>
+        <v>10722.89749389574</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46124.26941367686</v>
+        <v>46133.15724455935</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>10722.89975994197</v>
+        <v>10722.89660414125</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46124.31108034352</v>
+        <v>46133.19891122602</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>10722.89991542579</v>
+        <v>10722.89785250266</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46124.35274701018</v>
+        <v>46133.24057789268</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>10722.90205780944</v>
+        <v>10722.89993454139</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46124.39441367686</v>
+        <v>46133.28224455935</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>10722.90091338286</v>
+        <v>10722.89923385146</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46124.43608034352</v>
+        <v>46133.32391122602</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>10722.89747062301</v>
+        <v>10722.90242797557</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46124.47774701018</v>
+        <v>46133.36557789268</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>10722.89681579333</v>
+        <v>10722.89886692117</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46124.51941367686</v>
+        <v>46133.40724455935</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>10722.89637505839</v>
+        <v>10722.90360847744</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46124.56108034352</v>
+        <v>46133.44891122602</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>10722.90024515133</v>
+        <v>10722.90284643809</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46124.60274701018</v>
+        <v>46133.49057789268</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>10722.90531684987</v>
+        <v>10722.90467385069</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46124.64441367686</v>
+        <v>46133.53224455935</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>10722.90228183091</v>
+        <v>10722.90559877226</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46124.68608034352</v>
+        <v>46133.57391122602</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>10722.90264758247</v>
+        <v>10722.90602426518</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>

--- a/output/resultados_pipeline.xlsx
+++ b/output/resultados_pipeline.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cálculo pendiente (Métrica de severidad)</t>
+          <t>OK (0%)</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cálculo pendiente (Métrica de severidad)</t>
+          <t>OK (0%)</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cálculo pendiente (Métrica de severidad)</t>
+          <t>OK (0%)</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cálculo pendiente (Métrica de severidad)</t>
+          <t>OK (0%)</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cálculo pendiente (Métrica de severidad)</t>
+          <t>OK (0%)</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cálculo pendiente (Métrica de severidad)</t>
+          <t>OK (0%)</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cálculo pendiente (Métrica de severidad)</t>
+          <t>OK (0%)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>N/A (dato puntual)</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>N/A (dato puntual)</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>N/A (dato puntual)</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>N/A (dato puntual)</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>N/A (dato puntual)</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>N/A (dato puntual)</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>N/A (dato puntual)</t>
         </is>
       </c>
     </row>
@@ -934,17 +934,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pres_domo</t>
+          <t>1FSRPT501</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Variable no encontrada</t>
+          <t>Valido</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>La variable 'pres_domo' no esta en los datos</t>
+          <t>Cumple condicion &gt;= 0</t>
         </is>
       </c>
     </row>
@@ -956,17 +956,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pres_vap_sobrecal_a_turbina</t>
+          <t>1FSRPT504</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Variable no encontrada</t>
+          <t>Valido</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>La variable 'pres_vap_sobrecal_a_turbina' no esta en los datos</t>
+          <t>Cumple condicion &gt;= 0</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pres_vapor_entrada_recalentador</t>
+          <t>1FRSPT526</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Variable no encontrada</t>
+          <t>Valido</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>La variable 'pres_vapor_entrada_recalentador' no esta en los datos</t>
+          <t>Cumple condicion &gt;= 0</t>
         </is>
       </c>
     </row>
@@ -1000,17 +1000,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>temp_vapor_sobrecalentado_despues_atemperador_izq</t>
+          <t>1FSRTE502C</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Variable no encontrada</t>
+          <t>Valido</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>La variable 'temp_vapor_sobrecalentado_despues_atemperador_izq' no esta en los datos</t>
+          <t>Cumple condicion &lt;= 650</t>
         </is>
       </c>
     </row>
@@ -1022,17 +1022,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>temp_vapor_recalentado_salida_caldera</t>
+          <t>1FRSTE503A</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Variable no encontrada</t>
+          <t>Valido</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>La variable 'temp_vapor_recalentado_salida_caldera' no esta en los datos</t>
+          <t>Cumple condicion &lt;= 650</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Error de evaluacion</t>
+          <t>Consistente</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Variable 'flujo_vapor_sobrecalentado_cuerpo_ap_turbina' no encontrada</t>
+          <t>Si el flujo de vapor es muy bajo, la potencia debe ser cercana a cero.</t>
         </is>
       </c>
     </row>
